--- a/InputData/trans/GCApLC/Grams CO2e Avoided per LCFS Credit.xlsx
+++ b/InputData/trans/GCApLC/Grams CO2e Avoided per LCFS Credit.xlsx
@@ -1,30 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengpin.ge\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\trans\GCApLC\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4339663C70F76739F3FF6CA140434914EC568D6F" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12375" yWindow="1965" windowWidth="15645" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="27795" windowHeight="13875"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="GCApLC" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -76,7 +62,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -133,9 +119,6 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -183,7 +166,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -216,26 +199,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -268,23 +234,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -460,7 +409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -541,7 +490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -572,49 +521,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -622,24 +554,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -658,70 +651,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -823,40 +769,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{983E576D-F87D-4215-B1ED-8F80C835DE8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FC14BB5-EDD2-4239-9836-FFA0A0DA82AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C2FB7B2-257D-44EA-A6DA-7E9153614693}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C800F53-5994-465C-9839-C1619BF69BAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDAB32D0-8F9C-4CFC-ABA6-FF723819CA1E}"/>
 </file>